--- a/data/eval/S2_pre.xlsx
+++ b/data/eval/S2_pre.xlsx
@@ -5,17 +5,30 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apoorva.ajay\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apoorva.ajay\Downloads\ApoorvaThesis\ApoorvaThesis\enrichment_api\data\eval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E606016-9FAC-4373-9600-2396614FB8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE67B55-E621-4506-A3D5-D5E35D363595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -3720,7 +3733,10 @@
     <col min="8" max="8" width="31.5546875" customWidth="1"/>
     <col min="9" max="9" width="28.88671875" customWidth="1"/>
     <col min="10" max="10" width="20.109375" customWidth="1"/>
+    <col min="13" max="13" width="6.33203125" customWidth="1"/>
     <col min="14" max="14" width="29.77734375" customWidth="1"/>
+    <col min="15" max="15" width="35.77734375" customWidth="1"/>
+    <col min="16" max="17" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.3">
